--- a/documents/Blood-Relations.xlsx
+++ b/documents/Blood-Relations.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F791D9-1D07-4AC3-A949-E64A2E809A71}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E222598C-5419-40EF-A02B-C3E9B4492F62}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Blood Relation" sheetId="1" r:id="rId1"/>
+    <sheet name="Sample Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>You</t>
   </si>
@@ -88,12 +89,6 @@
     <t>Aunty</t>
   </si>
   <si>
-    <t>(Son/ Daughter)</t>
-  </si>
-  <si>
-    <t>Cousin</t>
-  </si>
-  <si>
     <t>Paternal</t>
   </si>
   <si>
@@ -113,6 +108,21 @@
   </si>
   <si>
     <t>(Husband)</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>Cousin Sister</t>
+  </si>
+  <si>
+    <t>Daughter</t>
+  </si>
+  <si>
+    <t>Cousin Daughter</t>
+  </si>
+  <si>
+    <t>Cousin Son</t>
   </si>
 </sst>
 </file>
@@ -208,15 +218,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,6 +510,7 @@
   <dimension ref="B5:M15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
@@ -514,49 +525,53 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="D5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>25</v>
+      <c r="D5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
-        <v>23</v>
+      <c r="B6" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="6" t="s">
+      <c r="B7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -567,17 +582,21 @@
       <c r="J7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -585,21 +604,21 @@
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5" t="s">
+      <c r="H10" s="11"/>
+      <c r="I10" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="J10" s="5"/>
+      <c r="J10" s="11"/>
       <c r="K10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M10" s="2"/>
@@ -612,17 +631,17 @@
       <c r="K11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>13</v>
       </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C12" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>3</v>
@@ -639,34 +658,34 @@
       <c r="K12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="E13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>4</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="2"/>
@@ -676,10 +695,10 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -691,4 +710,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD9A7954-9DA5-44F9-AA2D-A74CBB3D2DE3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>